--- a/results/results_diabetes_korea_simple.xlsx
+++ b/results/results_diabetes_korea_simple.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -437,92 +437,127 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>YLD_sex</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>PAF_med</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PAF_lo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PAF_hi</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>AC_med</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>AC_lo</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>AC_hi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>AD_med</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AD_lo</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AD_hi</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>YLD_med</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>YLD_lo</t>
+          <t>YLD_incidence_med</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>YLD_hi</t>
+          <t>YLD_incidence_lo</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>YLD_incidence_hi</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>YLD_prevalence_med</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>YLD_prevalence_lo</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>YLD_prevalence_hi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>YLL_med</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>YLL_lo</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>YLL_hi</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>DALY_med</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>DALY_lo</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>DALY_hi</t>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>DALY_incidence_med</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>DALY_incidence_lo</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>DALY_incidence_hi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>DALY_prevalence_med</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>DALY_prevalence_lo</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>DALY_prevalence_hi</t>
         </is>
       </c>
     </row>
@@ -539,34 +574,34 @@
         <v>0.06</v>
       </c>
       <c r="D2">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="E2">
         <v>0.43</v>
       </c>
       <c r="F2">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="H2">
         <v>5058</v>
       </c>
       <c r="I2">
-        <v>-1.660731206821651</v>
+        <v>-1.714798428091927</v>
       </c>
       <c r="J2">
         <v>1.459948535832434</v>
       </c>
       <c r="K2">
-        <v>0.938467460514304</v>
+        <v>0.9338381404521634</v>
       </c>
       <c r="L2">
-        <v>0.5515590672171771</v>
+        <v>0.5225296426267994</v>
       </c>
       <c r="M2">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="N2">
         <v>19.10000000000001</v>
@@ -578,58 +613,79 @@
         <v>13.16585805031761</v>
       </c>
       <c r="Q2">
-        <v>0.5870720902752697</v>
+        <v>8355.608426829789</v>
       </c>
       <c r="R2">
-        <v>0.1644894705132682</v>
+        <v>0.5655118872499525</v>
       </c>
       <c r="S2">
-        <v>0.7975996679104673</v>
+        <v>0.1748659382502645</v>
       </c>
       <c r="T2">
-        <v>2969.410632612315</v>
+        <v>0.7759762354111954</v>
       </c>
       <c r="U2">
-        <v>831.9877418561103</v>
+        <v>2860.359125710259</v>
       </c>
       <c r="V2">
-        <v>4034.259120291144</v>
+        <v>884.4719156698376</v>
       </c>
       <c r="W2">
-        <v>352.119969026204</v>
+        <v>3924.887798709826</v>
       </c>
       <c r="X2">
-        <v>98.6591395191531</v>
+        <v>339.188374853649</v>
       </c>
       <c r="Y2">
-        <v>478.3923048160191</v>
+        <v>104.8828411031261</v>
       </c>
       <c r="Z2">
-        <v>3768.174977300885</v>
+        <v>465.4227862372808</v>
       </c>
       <c r="AA2">
-        <v>1064.872579708965</v>
+        <v>3640.762118546997</v>
       </c>
       <c r="AB2">
-        <v>6217.576709408966</v>
+        <v>1070.675803783273</v>
       </c>
       <c r="AC2">
-        <v>4635.961528881237</v>
+        <v>6032.755508858303</v>
       </c>
       <c r="AD2">
-        <v>1298.93222627565</v>
+        <v>4725.19589057812</v>
       </c>
       <c r="AE2">
-        <v>6298.445177571983</v>
+        <v>1461.111307209407</v>
       </c>
       <c r="AF2">
-        <v>8464.562611046293</v>
+        <v>6483.753571621441</v>
       </c>
       <c r="AG2">
-        <v>2444.509306135591</v>
+        <v>4465.705995641061</v>
       </c>
       <c r="AH2">
-        <v>12254.99596989226</v>
+        <v>1380.872597877776</v>
+      </c>
+      <c r="AI2">
+        <v>6127.690336983356</v>
+      </c>
+      <c r="AJ2">
+        <v>8204.592613404653</v>
+      </c>
+      <c r="AK2">
+        <v>2533.328470955399</v>
+      </c>
+      <c r="AL2">
+        <v>11979.48258204531</v>
+      </c>
+      <c r="AM2">
+        <v>9190.901886219181</v>
+      </c>
+      <c r="AN2">
+        <v>2841.983905087183</v>
+      </c>
+      <c r="AO2">
+        <v>12611.4439086048</v>
       </c>
     </row>
     <row r="3">
@@ -642,37 +698,37 @@
         <v>0.02</v>
       </c>
       <c r="C3">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D3">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="E3">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="F3">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="G3">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="H3">
         <v>8084</v>
       </c>
       <c r="I3">
-        <v>-1.514127732629776</v>
+        <v>-1.237874356001617</v>
       </c>
       <c r="J3">
-        <v>1.222152467927124</v>
+        <v>1.274879246944082</v>
       </c>
       <c r="K3">
-        <v>0.9751202882482998</v>
+        <v>0.9820284327342864</v>
       </c>
       <c r="L3">
-        <v>0.4642651689432709</v>
+        <v>0.6536287110426722</v>
       </c>
       <c r="M3">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="N3">
         <v>17.8</v>
@@ -684,58 +740,79 @@
         <v>16.50964166219702</v>
       </c>
       <c r="Q3">
-        <v>0.646384793833898</v>
+        <v>13225.90447579696</v>
       </c>
       <c r="R3">
-        <v>0.2270728566173505</v>
+        <v>0.7740105214427841</v>
       </c>
       <c r="S3">
-        <v>0.8546410213867927</v>
+        <v>0.1875409158649912</v>
       </c>
       <c r="T3">
-        <v>5225.374673353232</v>
+        <v>0.9254013542795342</v>
       </c>
       <c r="U3">
-        <v>1835.656972894662</v>
+        <v>6257.101055343466</v>
       </c>
       <c r="V3">
-        <v>6908.918016890832</v>
+        <v>1516.080763852588</v>
       </c>
       <c r="W3">
-        <v>506.1580766595721</v>
+        <v>7480.944547995755</v>
       </c>
       <c r="X3">
-        <v>177.8116711027825</v>
+        <v>606.0966789209865</v>
       </c>
       <c r="Y3">
-        <v>669.2351982071419</v>
+        <v>146.85578957724</v>
       </c>
       <c r="Z3">
-        <v>6195.163717159534</v>
+        <v>724.644784482132</v>
       </c>
       <c r="AA3">
-        <v>2036.357242052048</v>
+        <v>7251.602020337377</v>
       </c>
       <c r="AB3">
-        <v>10024.02160761988</v>
+        <v>1952.634662941015</v>
       </c>
       <c r="AC3">
-        <v>8356.488470076387</v>
+        <v>11345.60598622314</v>
       </c>
       <c r="AD3">
-        <v>2935.606973263372</v>
+        <v>10236.98921986406</v>
       </c>
       <c r="AE3">
-        <v>11048.83331012931</v>
+        <v>2480.398238533848</v>
       </c>
       <c r="AF3">
-        <v>14700.37930785513</v>
+        <v>12239.26991347426</v>
       </c>
       <c r="AG3">
-        <v>5116.256551601713</v>
+        <v>10006.43898163317</v>
       </c>
       <c r="AH3">
-        <v>20524.10064557077</v>
+        <v>2424.53646193924</v>
+      </c>
+      <c r="AI3">
+        <v>11963.62572417999</v>
+      </c>
+      <c r="AJ3">
+        <v>17313.6241591019</v>
+      </c>
+      <c r="AK3">
+        <v>4279.892376844336</v>
+      </c>
+      <c r="AL3">
+        <v>22628.46370817224</v>
+      </c>
+      <c r="AM3">
+        <v>20243.42820149723</v>
+      </c>
+      <c r="AN3">
+        <v>4904.934700473089</v>
+      </c>
+      <c r="AO3">
+        <v>24202.89563765425</v>
       </c>
     </row>
   </sheetData>

--- a/results/results_diabetes_korea_simple.xlsx
+++ b/results/results_diabetes_korea_simple.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO3"/>
+  <dimension ref="A1:AR3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,140 +422,155 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>med_cap</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>D_years</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>seyll</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>YLD_sex</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>YLD_mode</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>YLD_lower</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>YLD_upper</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>PAF_med</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>PAF_lo</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>PAF_hi</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>AC_med</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AC_lo</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AC_hi</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>AD_med</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>AD_lo</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>AD_hi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>YLD_incidence_med</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>YLD_incidence_lo</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>YLD_incidence_hi</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>YLD_prevalence_med</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>YLD_prevalence_lo</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>YLD_prevalence_hi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>YLL_med</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>YLL_lo</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>YLL_hi</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>DALY_incidence_med</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>DALY_incidence_lo</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DALY_incidence_hi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>DALY_prevalence_med</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>DALY_prevalence_lo</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>DALY_prevalence_hi</t>
         </is>
@@ -604,88 +619,97 @@
         <v>0.18</v>
       </c>
       <c r="N2">
+        <v>0.1732661337461954</v>
+      </c>
+      <c r="O2">
         <v>19.10000000000001</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>599.79</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>13.16585805031761</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>8355.608426829789</v>
       </c>
-      <c r="R2">
-        <v>0.5655118872499525</v>
-      </c>
       <c r="S2">
-        <v>0.1748659382502645</v>
+        <v>5617.300593266269</v>
       </c>
       <c r="T2">
-        <v>0.7759762354111954</v>
+        <v>11465.14910195645</v>
       </c>
       <c r="U2">
-        <v>2860.359125710259</v>
+        <v>0.5468342732675411</v>
       </c>
       <c r="V2">
-        <v>884.4719156698376</v>
+        <v>0.1230068841019617</v>
       </c>
       <c r="W2">
-        <v>3924.887798709826</v>
+        <v>0.7571894554780508</v>
       </c>
       <c r="X2">
-        <v>339.188374853649</v>
+        <v>2765.887754187223</v>
       </c>
       <c r="Y2">
-        <v>104.8828411031261</v>
+        <v>622.1688197877224</v>
       </c>
       <c r="Z2">
-        <v>465.4227862372808</v>
+        <v>3829.864265807981</v>
       </c>
       <c r="AA2">
-        <v>3640.762118546997</v>
+        <v>327.9857287631385</v>
       </c>
       <c r="AB2">
-        <v>1070.675803783273</v>
+        <v>73.77829901551563</v>
       </c>
       <c r="AC2">
-        <v>6032.755508858303</v>
+        <v>454.15466350118</v>
       </c>
       <c r="AD2">
-        <v>4725.19589057812</v>
+        <v>3534.187397499984</v>
       </c>
       <c r="AE2">
-        <v>1461.111307209407</v>
+        <v>761.8226371799839</v>
       </c>
       <c r="AF2">
-        <v>6483.753571621441</v>
+        <v>5939.730529890795</v>
       </c>
       <c r="AG2">
-        <v>4465.705995641061</v>
+        <v>4463.571812799732</v>
       </c>
       <c r="AH2">
-        <v>1380.872597877776</v>
+        <v>1003.932538464221</v>
       </c>
       <c r="AI2">
-        <v>6127.690336983356</v>
+        <v>6867.83710839018</v>
       </c>
       <c r="AJ2">
-        <v>8204.592613404653</v>
+        <v>4318.213547425456</v>
       </c>
       <c r="AK2">
-        <v>2533.328470955399</v>
+        <v>971.3546120321663</v>
       </c>
       <c r="AL2">
-        <v>11979.48258204531</v>
+        <v>5979.335832546297</v>
       </c>
       <c r="AM2">
-        <v>9190.901886219181</v>
+        <v>7886.036904286856</v>
       </c>
       <c r="AN2">
-        <v>2841.983905087183</v>
+        <v>1708.77613265136</v>
       </c>
       <c r="AO2">
-        <v>12611.4439086048</v>
+        <v>11727.27152943065</v>
+      </c>
+      <c r="AP2">
+        <v>8802.430707795733</v>
+      </c>
+      <c r="AQ2">
+        <v>1944.400772079556</v>
+      </c>
+      <c r="AR2">
+        <v>12601.50711886464</v>
       </c>
     </row>
     <row r="3">
@@ -731,88 +755,97 @@
         <v>0.29</v>
       </c>
       <c r="N3">
+        <v>0.1732661337461954</v>
+      </c>
+      <c r="O3">
         <v>17.8</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>783.0599999999999</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>16.50964166219702</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>13225.90447579696</v>
       </c>
-      <c r="R3">
-        <v>0.7740105214427841</v>
-      </c>
       <c r="S3">
-        <v>0.1875409158649912</v>
+        <v>8916.644865520693</v>
       </c>
       <c r="T3">
-        <v>0.9254013542795342</v>
+        <v>17957.83716914366</v>
       </c>
       <c r="U3">
-        <v>6257.101055343466</v>
+        <v>0.5570496113494856</v>
       </c>
       <c r="V3">
-        <v>1516.080763852588</v>
+        <v>0.187649500168478</v>
       </c>
       <c r="W3">
-        <v>7480.944547995755</v>
+        <v>0.7777807203980891</v>
       </c>
       <c r="X3">
-        <v>606.0966789209865</v>
+        <v>4503.189058149241</v>
       </c>
       <c r="Y3">
-        <v>146.85578957724</v>
+        <v>1516.958559361976</v>
       </c>
       <c r="Z3">
-        <v>724.644784482132</v>
+        <v>6287.579343698152</v>
       </c>
       <c r="AA3">
-        <v>7251.602020337377</v>
+        <v>436.2032686633281</v>
       </c>
       <c r="AB3">
-        <v>1952.634662941015</v>
+        <v>146.9408176019284</v>
       </c>
       <c r="AC3">
-        <v>11345.60598622314</v>
+        <v>609.0489709149276</v>
       </c>
       <c r="AD3">
-        <v>10236.98921986406</v>
+        <v>5354.774938319879</v>
       </c>
       <c r="AE3">
-        <v>2480.398238533848</v>
+        <v>1767.869300135417</v>
       </c>
       <c r="AF3">
-        <v>12239.26991347426</v>
+        <v>8857.201371976022</v>
       </c>
       <c r="AG3">
-        <v>10006.43898163317</v>
+        <v>7200.212603762933</v>
       </c>
       <c r="AH3">
-        <v>2424.53646193924</v>
+        <v>2289.962316690566</v>
       </c>
       <c r="AI3">
-        <v>11963.62572417999</v>
+        <v>11366.62840959124</v>
       </c>
       <c r="AJ3">
-        <v>17313.6241591019</v>
+        <v>7201.559657510604</v>
       </c>
       <c r="AK3">
-        <v>4279.892376844336</v>
+        <v>2425.94024415809</v>
       </c>
       <c r="AL3">
-        <v>22628.46370817224</v>
+        <v>10055.18026453531</v>
       </c>
       <c r="AM3">
-        <v>20243.42820149723</v>
+        <v>12667.3265505709</v>
       </c>
       <c r="AN3">
-        <v>4904.934700473089</v>
+        <v>4266.350013160704</v>
       </c>
       <c r="AO3">
-        <v>24202.89563765425</v>
+        <v>18169.03426244861</v>
+      </c>
+      <c r="AP3">
+        <v>14488.1320491846</v>
+      </c>
+      <c r="AQ3">
+        <v>4822.265981414587</v>
+      </c>
+      <c r="AR3">
+        <v>21063.46575576582</v>
       </c>
     </row>
   </sheetData>

--- a/results/results_diabetes_korea_simple.xlsx
+++ b/results/results_diabetes_korea_simple.xlsx
@@ -640,76 +640,76 @@
         <v>11465.14910195645</v>
       </c>
       <c r="U2">
-        <v>0.5468342732675411</v>
+        <v>0.5626339226910462</v>
       </c>
       <c r="V2">
-        <v>0.1230068841019617</v>
+        <v>0.1280886104065338</v>
       </c>
       <c r="W2">
-        <v>0.7571894554780508</v>
+        <v>0.772171860210397</v>
       </c>
       <c r="X2">
-        <v>2765.887754187223</v>
+        <v>2845.802380971312</v>
       </c>
       <c r="Y2">
-        <v>622.1688197877224</v>
+        <v>647.8721914362479</v>
       </c>
       <c r="Z2">
-        <v>3829.864265807981</v>
+        <v>3905.645268944188</v>
       </c>
       <c r="AA2">
-        <v>327.9857287631385</v>
+        <v>337.4622004908626</v>
       </c>
       <c r="AB2">
-        <v>73.77829901551563</v>
+        <v>76.82626763573489</v>
       </c>
       <c r="AC2">
-        <v>454.15466350118</v>
+        <v>463.140960035594</v>
       </c>
       <c r="AD2">
-        <v>3534.187397499984</v>
+        <v>3638.316941053125</v>
       </c>
       <c r="AE2">
-        <v>761.8226371799839</v>
+        <v>792.6225607539411</v>
       </c>
       <c r="AF2">
-        <v>5939.730529890795</v>
+        <v>6071.02065202613</v>
       </c>
       <c r="AG2">
-        <v>4463.571812799732</v>
+        <v>4591.302964718424</v>
       </c>
       <c r="AH2">
-        <v>1003.932538464221</v>
+        <v>1045.256178325193</v>
       </c>
       <c r="AI2">
-        <v>6867.83710839018</v>
+        <v>7023.549035497175</v>
       </c>
       <c r="AJ2">
-        <v>4318.213547425456</v>
+        <v>4442.979429010519</v>
       </c>
       <c r="AK2">
-        <v>971.3546120321663</v>
+        <v>1011.483734227796</v>
       </c>
       <c r="AL2">
-        <v>5979.335832546297</v>
+        <v>6097.648137116453</v>
       </c>
       <c r="AM2">
-        <v>7886.036904286856</v>
+        <v>8114.317764140971</v>
       </c>
       <c r="AN2">
-        <v>1708.77613265136</v>
+        <v>1779.37003733522</v>
       </c>
       <c r="AO2">
-        <v>11727.27152943065</v>
+        <v>11954.11121717787</v>
       </c>
       <c r="AP2">
-        <v>8802.430707795733</v>
+        <v>9060.469984392526</v>
       </c>
       <c r="AQ2">
-        <v>1944.400772079556</v>
+        <v>2025.056148708639</v>
       </c>
       <c r="AR2">
-        <v>12601.50711886464</v>
+        <v>12859.15632227164</v>
       </c>
     </row>
     <row r="3">
@@ -776,76 +776,76 @@
         <v>17957.83716914366</v>
       </c>
       <c r="U3">
-        <v>0.5570496113494856</v>
+        <v>0.763203335786143</v>
       </c>
       <c r="V3">
-        <v>0.187649500168478</v>
+        <v>0.3072384518700522</v>
       </c>
       <c r="W3">
-        <v>0.7777807203980891</v>
+        <v>0.9301545503078142</v>
       </c>
       <c r="X3">
-        <v>4503.189058149241</v>
+        <v>6169.73576649518</v>
       </c>
       <c r="Y3">
-        <v>1516.958559361976</v>
+        <v>2483.715644917502</v>
       </c>
       <c r="Z3">
-        <v>6287.579343698152</v>
+        <v>7519.369384688371</v>
       </c>
       <c r="AA3">
-        <v>436.2032686633281</v>
+        <v>597.634004120697</v>
       </c>
       <c r="AB3">
-        <v>146.9408176019284</v>
+        <v>240.586142121363</v>
       </c>
       <c r="AC3">
-        <v>609.0489709149276</v>
+        <v>728.3668221640369</v>
       </c>
       <c r="AD3">
-        <v>5354.774938319879</v>
+        <v>7347.742171011835</v>
       </c>
       <c r="AE3">
-        <v>1767.869300135417</v>
+        <v>2846.69701371751</v>
       </c>
       <c r="AF3">
-        <v>8857.201371976022</v>
+        <v>11166.23275331706</v>
       </c>
       <c r="AG3">
-        <v>7200.212603762933</v>
+        <v>9815.938980283803</v>
       </c>
       <c r="AH3">
-        <v>2289.962316690566</v>
+        <v>3749.300015655776</v>
       </c>
       <c r="AI3">
-        <v>11366.62840959124</v>
+        <v>13876.02562812383</v>
       </c>
       <c r="AJ3">
-        <v>7201.559657510604</v>
+        <v>9866.723253176686</v>
       </c>
       <c r="AK3">
-        <v>2425.94024415809</v>
+        <v>3971.990995314109</v>
       </c>
       <c r="AL3">
-        <v>10055.18026453531</v>
+        <v>12025.07523256143</v>
       </c>
       <c r="AM3">
-        <v>12667.3265505709</v>
+        <v>17293.41545589716</v>
       </c>
       <c r="AN3">
-        <v>4266.350013160704</v>
+        <v>6980.689862345132</v>
       </c>
       <c r="AO3">
-        <v>18169.03426244861</v>
+        <v>22476.89932761834</v>
       </c>
       <c r="AP3">
-        <v>14488.1320491846</v>
+        <v>19805.23058118445</v>
       </c>
       <c r="AQ3">
-        <v>4822.265981414587</v>
+        <v>7811.367795505657</v>
       </c>
       <c r="AR3">
-        <v>21063.46575576582</v>
+        <v>25651.80266011236</v>
       </c>
     </row>
   </sheetData>

--- a/results/results_diabetes_korea_simple.xlsx
+++ b/results/results_diabetes_korea_simple.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR3"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -457,120 +457,150 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>prev_mode</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prev_lower</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>prev_upper</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>PAF_med</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PAF_lo</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PAF_hi</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>AC_med</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>AC_lo</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>AC_hi</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>AI_med</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>AI_lo</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>AI_hi</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>AP_med</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>AP_lo</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>AP_hi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>AD_med</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>AD_lo</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>AD_hi</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>YLD_incidence_med</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>YLD_incidence_lo</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>YLD_incidence_hi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>YLD_prevalence_med</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>YLD_prevalence_lo</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>YLD_prevalence_hi</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>YLL_med</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>YLL_lo</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>YLL_hi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>DALY_incidence_med</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>DALY_incidence_lo</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>DALY_incidence_hi</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>DALY_prevalence_med</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>DALY_prevalence_lo</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>DALY_prevalence_hi</t>
         </is>
@@ -640,76 +670,94 @@
         <v>11465.14910195645</v>
       </c>
       <c r="U2">
-        <v>0.5626339226910462</v>
+        <v>122399.7379515309</v>
       </c>
       <c r="V2">
-        <v>0.1280886104065338</v>
+        <v>111088.0815936342</v>
       </c>
       <c r="W2">
-        <v>0.772171860210397</v>
+        <v>134597.2119864031</v>
       </c>
       <c r="X2">
-        <v>2845.802380971312</v>
+        <v>0.5610707671113333</v>
       </c>
       <c r="Y2">
-        <v>647.8721914362479</v>
+        <v>0.1495637558332405</v>
       </c>
       <c r="Z2">
-        <v>3905.645268944188</v>
+        <v>0.7745663655423909</v>
       </c>
       <c r="AA2">
-        <v>337.4622004908626</v>
+        <v>2837.895940049124</v>
       </c>
       <c r="AB2">
-        <v>76.82626763573489</v>
+        <v>756.4934770045304</v>
       </c>
       <c r="AC2">
-        <v>463.140960035594</v>
+        <v>3917.756676913413</v>
       </c>
       <c r="AD2">
-        <v>3638.316941053125</v>
+        <v>68950.34397596522</v>
       </c>
       <c r="AE2">
-        <v>792.6225607539411</v>
+        <v>18259.23977360543</v>
       </c>
       <c r="AF2">
-        <v>6071.02065202613</v>
+        <v>95608.6306350446</v>
       </c>
       <c r="AG2">
-        <v>4591.302964718424</v>
+        <v>336.5246354057065</v>
       </c>
       <c r="AH2">
-        <v>1045.256178325193</v>
+        <v>89.70684511121931</v>
       </c>
       <c r="AI2">
-        <v>7023.549035497175</v>
+        <v>464.5771603886706</v>
       </c>
       <c r="AJ2">
-        <v>4442.979429010519</v>
+        <v>3682.878927682212</v>
       </c>
       <c r="AK2">
-        <v>1011.483734227796</v>
+        <v>883.9051004691061</v>
       </c>
       <c r="AL2">
-        <v>6097.648137116453</v>
+        <v>5882.86878988441</v>
       </c>
       <c r="AM2">
-        <v>8114.317764140971</v>
+        <v>4632.588999843947</v>
       </c>
       <c r="AN2">
-        <v>1779.37003733522</v>
+        <v>1199.125519281069</v>
       </c>
       <c r="AO2">
-        <v>11954.11121717787</v>
+        <v>7176.397590090946</v>
       </c>
       <c r="AP2">
-        <v>9060.469984392526</v>
+        <v>4430.635580186421</v>
       </c>
       <c r="AQ2">
-        <v>2025.056148708639</v>
+        <v>1181.067588876142</v>
       </c>
       <c r="AR2">
-        <v>12859.15632227164</v>
+        <v>6116.556947096876</v>
+      </c>
+      <c r="AS2">
+        <v>8222.644629055496</v>
+      </c>
+      <c r="AT2">
+        <v>2041.247552515236</v>
+      </c>
+      <c r="AU2">
+        <v>11936.80932784461</v>
+      </c>
+      <c r="AV2">
+        <v>9125.729051859669</v>
+      </c>
+      <c r="AW2">
+        <v>2350.552759497909</v>
+      </c>
+      <c r="AX2">
+        <v>13173.33604395714</v>
       </c>
     </row>
     <row r="3">
@@ -776,76 +824,94 @@
         <v>17957.83716914366</v>
       </c>
       <c r="U3">
-        <v>0.763203335786143</v>
+        <v>194510.8828933874</v>
       </c>
       <c r="V3">
-        <v>0.3072384518700522</v>
+        <v>169049.8026957066</v>
       </c>
       <c r="W3">
-        <v>0.9301545503078142</v>
+        <v>211790.4427773821</v>
       </c>
       <c r="X3">
-        <v>6169.73576649518</v>
+        <v>0.7662638871838636</v>
       </c>
       <c r="Y3">
-        <v>2483.715644917502</v>
+        <v>0.2405199893742356</v>
       </c>
       <c r="Z3">
-        <v>7519.369384688371</v>
+        <v>0.9227680972539796</v>
       </c>
       <c r="AA3">
-        <v>597.634004120697</v>
+        <v>6194.477263994353</v>
       </c>
       <c r="AB3">
-        <v>240.586142121363</v>
+        <v>1944.363594101321</v>
       </c>
       <c r="AC3">
-        <v>728.3668221640369</v>
+        <v>7459.657298201171</v>
       </c>
       <c r="AD3">
-        <v>7347.742171011835</v>
+        <v>148814.4200246374</v>
       </c>
       <c r="AE3">
-        <v>2846.69701371751</v>
+        <v>46047.36410167311</v>
       </c>
       <c r="AF3">
-        <v>11166.23275331706</v>
+        <v>181880.9233238286</v>
       </c>
       <c r="AG3">
-        <v>9815.938980283803</v>
+        <v>600.0305994981962</v>
       </c>
       <c r="AH3">
-        <v>3749.300015655776</v>
+        <v>188.3415828793889</v>
       </c>
       <c r="AI3">
-        <v>13876.02562812383</v>
+        <v>722.5827862357013</v>
       </c>
       <c r="AJ3">
-        <v>9866.723253176686</v>
+        <v>7404.376474190285</v>
       </c>
       <c r="AK3">
-        <v>3971.990995314109</v>
+        <v>2483.688781402777</v>
       </c>
       <c r="AL3">
-        <v>12025.07523256143</v>
+        <v>11122.10459891088</v>
       </c>
       <c r="AM3">
-        <v>17293.41545589716</v>
+        <v>9855.253842631671</v>
       </c>
       <c r="AN3">
-        <v>6980.689862345132</v>
+        <v>3423.590825829551</v>
       </c>
       <c r="AO3">
-        <v>22476.89932761834</v>
+        <v>13920.85069251943</v>
       </c>
       <c r="AP3">
-        <v>19805.23058118445</v>
+        <v>9906.290184068477</v>
       </c>
       <c r="AQ3">
-        <v>7811.367795505657</v>
+        <v>3109.452043429693</v>
       </c>
       <c r="AR3">
-        <v>25651.80266011236</v>
+        <v>11929.58287202334</v>
+      </c>
+      <c r="AS3">
+        <v>17333.54716179446</v>
+      </c>
+      <c r="AT3">
+        <v>5421.630967981735</v>
+      </c>
+      <c r="AU3">
+        <v>22811.31017845288</v>
+      </c>
+      <c r="AV3">
+        <v>19946.11680292777</v>
+      </c>
+      <c r="AW3">
+        <v>6546.03264533469</v>
+      </c>
+      <c r="AX3">
+        <v>25595.22238837936</v>
       </c>
     </row>
   </sheetData>
